--- a/AAII_Financials/Quarterly/DH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>DH</t>
   </si>
@@ -656,212 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E8" s="3">
         <v>55900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>61500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>60000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>60800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>62700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>63500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>59200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>60600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>54500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>50100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>46300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>43100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>76800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>26300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -869,165 +876,171 @@
         <v>9400</v>
       </c>
       <c r="E9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F9" s="3">
         <v>9900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7300</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>7400</v>
       </c>
       <c r="AC9" s="3">
         <v>7400</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E10" s="3">
         <v>46600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>51000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>49100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>52600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>53800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>53700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>56500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>56700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>52900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>50600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>50800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>47700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>35400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>32600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>47600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,74 +1070,75 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>10100</v>
       </c>
       <c r="L12" s="3">
         <v>10100</v>
       </c>
       <c r="M12" s="3">
+        <v>10100</v>
+      </c>
+      <c r="N12" s="3">
         <v>11600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8100</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,74 +1240,77 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>196500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>178300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>99900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>226200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>366500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>290900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1306,74 +1326,77 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E15" s="3">
         <v>13200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>13100</v>
       </c>
       <c r="J15" s="3">
         <v>13100</v>
       </c>
       <c r="K15" s="3">
+        <v>13100</v>
+      </c>
+      <c r="L15" s="3">
         <v>12800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>13000</v>
       </c>
       <c r="N15" s="3">
         <v>13000</v>
       </c>
       <c r="O15" s="3">
+        <v>13000</v>
+      </c>
+      <c r="P15" s="3">
         <v>12800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12900</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>10000</v>
       </c>
       <c r="R15" s="3">
         <v>10000</v>
       </c>
       <c r="S15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="T15" s="3">
         <v>10200</v>
-      </c>
-      <c r="T15" s="3">
-        <v>9900</v>
       </c>
       <c r="U15" s="3">
         <v>9900</v>
       </c>
       <c r="V15" s="3">
+        <v>9900</v>
+      </c>
+      <c r="W15" s="3">
         <v>9800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>19100</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,74 +1443,75 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E17" s="3">
         <v>60800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>68200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>66200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>62000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>66900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>71200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>69500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>68900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>73000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>66400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>58500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>85500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1500,74 +1527,77 @@
       <c r="AC17" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1583,8 +1613,11 @@
       <c r="AC18" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,73 +1647,74 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-41600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-29600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>8</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>8</v>
@@ -1697,74 +1731,77 @@
       <c r="AC20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>15200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>20800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1789,65 +1829,65 @@
         <v>2600</v>
       </c>
       <c r="E22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F22" s="3">
         <v>2900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3000</v>
       </c>
       <c r="G22" s="3">
         <v>3000</v>
       </c>
       <c r="H22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I22" s="3">
         <v>2400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3800</v>
       </c>
       <c r="L22" s="3">
         <v>3800</v>
       </c>
       <c r="M22" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="N22" s="3">
         <v>3900</v>
       </c>
       <c r="O22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="P22" s="3">
         <v>3800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1863,74 +1903,77 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-195800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-166000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-90600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-201500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-328100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-266200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-25500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1946,68 +1989,71 @@
       <c r="AC23" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
       </c>
       <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
         <v>-10900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-21900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-17500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-17600</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>8</v>
       </c>
@@ -2020,8 +2066,8 @@
       <c r="Z24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,74 +2161,77 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-192400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-155100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-84700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-187800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-306200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-248700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-25500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2195,73 +2247,76 @@
       <c r="AC26" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-138600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-107200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-59100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-130900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-213600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-171500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>8</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>8</v>
@@ -2278,8 +2333,11 @@
       <c r="AC27" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,73 +2677,76 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>41600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>29600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>8</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>8</v>
@@ -2693,73 +2763,76 @@
       <c r="AC32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-138600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-107200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-59100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-130900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-213600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-171500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>8</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>8</v>
@@ -2776,8 +2849,11 @@
       <c r="AC33" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,73 +2935,76 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-138600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-107200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-59100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-130900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-213600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-171500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>8</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>8</v>
@@ -2942,96 +3021,102 @@
       <c r="AC35" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,80 +3178,81 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E41" s="3">
         <v>157600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>163600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>81000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>137600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>106000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>131000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>125000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>146900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>228800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>228200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>229800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>387500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>189800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z41" s="3">
         <v>24800</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3175,65 +3262,68 @@
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E42" s="3">
         <v>20600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>103400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>94600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>185600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>169200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>178500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>192900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>180500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>233800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>222700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>222400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>184900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>120800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>118200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>109000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3249,8 +3339,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3258,80 +3348,83 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E43" s="3">
         <v>39400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>54000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>56700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>59200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>51800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>38500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>43300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>22800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="3">
         <v>33100</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3385,8 +3481,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3424,80 +3520,83 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E45" s="3">
         <v>12400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>12800</v>
       </c>
       <c r="F45" s="3">
         <v>12800</v>
       </c>
       <c r="G45" s="3">
+        <v>12800</v>
+      </c>
+      <c r="H45" s="3">
         <v>13200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>13700</v>
       </c>
       <c r="I45" s="3">
         <v>13700</v>
       </c>
       <c r="J45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K45" s="3">
         <v>13500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>18900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>6000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3507,80 +3606,83 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>240100</v>
+      </c>
+      <c r="E46" s="3">
         <v>245800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>257600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>273400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>370200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>368700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>368300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>378700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>393900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>375400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>421000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>421500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>413700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>402200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>396200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>392200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>444200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>226600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>69500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z46" s="3">
         <v>63800</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3599,20 +3704,20 @@
         <v>600</v>
       </c>
       <c r="E47" s="3">
+        <v>600</v>
+      </c>
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3622,21 +3727,21 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1700</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -3647,11 +3752,11 @@
         <v>0</v>
       </c>
       <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>32700</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3664,8 +3769,8 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3673,80 +3778,83 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E48" s="3">
         <v>18700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4300</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="3">
         <v>3200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3756,80 +3864,83 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E49" s="3">
         <v>235400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>444700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>476800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>488000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>501500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>691200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>784900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1025500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1400100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1398200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1410000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1650500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1663000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1675500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1684700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1695200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1710800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1613900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1628200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1642800</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z49" s="3">
         <v>1671700</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,80 +4122,83 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
       </c>
       <c r="M52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3">
         <v>6600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>496800</v>
+      </c>
+      <c r="E54" s="3">
         <v>514700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>735500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>755500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>770100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>808700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1089400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1181700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1422400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1810100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1825900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1819500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2104900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2116900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2122600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2119800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2122900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2141700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2116000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1869800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1729500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1737800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1745400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1702700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1724600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1735200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1721200</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,80 +4446,81 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z57" s="3">
         <v>5700</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4414,40 +4548,40 @@
         <v>11400</v>
       </c>
       <c r="G58" s="3">
-        <v>11200</v>
+        <v>11400</v>
       </c>
       <c r="H58" s="3">
         <v>11200</v>
       </c>
       <c r="I58" s="3">
-        <v>16200</v>
+        <v>11200</v>
       </c>
       <c r="J58" s="3">
         <v>16200</v>
       </c>
       <c r="K58" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="L58" s="3">
         <v>16100</v>
       </c>
       <c r="M58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="N58" s="3">
         <v>16000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8600</v>
-      </c>
-      <c r="R58" s="3">
-        <v>6900</v>
       </c>
       <c r="S58" s="3">
         <v>6900</v>
@@ -4462,17 +4596,17 @@
         <v>6900</v>
       </c>
       <c r="W58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="X58" s="3">
         <v>4700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3">
         <v>4700</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4482,80 +4616,83 @@
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E59" s="3">
         <v>113300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>120700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>122600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>125400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>118800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>105100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>116600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>126600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>103800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>112200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>116600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>104400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>105600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>108900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>106300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>89100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>89400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z59" s="3">
         <v>78400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4565,80 +4702,83 @@
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E60" s="3">
         <v>140400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>156800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>153900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>151300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>156100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>161200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>148200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>153500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>165000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>170700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>147100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>148100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>151200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>140600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>121600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>119200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>122000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>117800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>98600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z60" s="3">
         <v>88700</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4648,80 +4788,83 @@
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E61" s="3">
         <v>158400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>164000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>166700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>169400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>237000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>240900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>244100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>248000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>251900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>255700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>258200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>262000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>255800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>259100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>260600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>262200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>263800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>265400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>455800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>457200</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4731,80 +4874,83 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E62" s="3">
         <v>14000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>59000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>66200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>93900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>135600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>136900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>147700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>164400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>161400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>244300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>261600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>254300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>260200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>231100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>218300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="3">
         <v>3900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>309000</v>
+      </c>
+      <c r="E66" s="3">
         <v>324000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>356500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>365900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>358900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>372800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>482200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>486100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>536100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>615100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>626700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>616100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>649400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>653000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1173700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1187000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1222400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1267500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1242800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1176900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>555100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>552200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>549800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>522500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>532900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>532400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>504900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,80 +5680,83 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-923500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-918100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-779500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-770200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-755400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-747800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-640600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-581500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-450600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-237000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-227500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-217200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-45700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-34100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-31500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-26300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-17700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-138700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-109900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,80 +6024,83 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E76" s="3">
         <v>146200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>281100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>284900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>303600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>322800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>444400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>506500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>644800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>860300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>861400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>863300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1008400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>984500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>948900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>932800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>900500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>874200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>873200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>692900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1174400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z76" s="3">
         <v>1195600</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,161 +6196,167 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-138600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-107200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-59100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-130900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-213600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-171500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>8</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>8</v>
@@ -6178,8 +6373,11 @@
       <c r="AC81" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,19 +6407,20 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>600</v>
@@ -6233,13 +6432,13 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -6248,35 +6447,35 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>500</v>
+      </c>
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>29600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E89" s="3">
         <v>11600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2300</v>
       </c>
       <c r="G91" s="3">
         <v>-2300</v>
       </c>
       <c r="H91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-7700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-800</v>
       </c>
       <c r="T91" s="3">
         <v>-800</v>
       </c>
       <c r="U91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>56400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>83500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>54400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-33500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-67900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-166900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7228,8 +7462,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,141 +7759,147 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-24700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-109700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>234700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>152800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>23900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
@@ -7662,10 +7911,10 @@
         <v>-100</v>
       </c>
       <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
@@ -7682,74 +7931,77 @@
       <c r="AC101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>55300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-32200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-54900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-81900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-157700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>197700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>151300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>8</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
